--- a/reports/pdf_rolling5_20260918.xlsx
+++ b/reports/pdf_rolling5_20260918.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,609억   ·   현금 86억(1.8%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 11종목  /  매도 18종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,609억   ·   현금 57억(1.2%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 11종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -1338,7 +1338,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,398억   ·   현금 178억(5.1%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 0종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,398억   ·   현금 118억(3.4%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1455,7 +1455,7 @@
     <row r="30" ht="19" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,547억   ·   현금 113억(4.3%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 3종목  /  매도 4종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,547억   ·   현금 76억(2.9%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 3종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B30" s="4" t="n"/>
@@ -1653,23 +1653,23 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-475695014</v>
+        <v>-2086920061</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.44%</t>
+          <t>6.12%→4.99%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>50→35</t>
+          <t>105→90</t>
         </is>
       </c>
     </row>
@@ -1681,30 +1681,30 @@
       <c r="E36" s="17" t="n"/>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-2086920061</v>
+        <v>-475695014</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>6.12%→4.99%</t>
+          <t>0.65%→0.44%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>105→90</t>
+          <t>50→35</t>
         </is>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,962억   ·   현금 38억(1.9%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,962억   ·   현금 26억(1.3%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -1969,7 +1969,7 @@
     <row r="46" ht="19" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억   ·   현금 5억(1.7%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 7종목  /  매도 4종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 280억   ·   현금 3억(1.2%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 7종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B46" s="4" t="n"/>
@@ -2318,7 +2318,7 @@
     <row r="57" ht="19" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 486억   ·   현금 8억(1.7%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 3종목  /  매도 3종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 486억   ·   현금 5억(1.1%)      오늘 2026-09-18  vs  5일전 2026-09-11      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B57" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260918.xlsx
+++ b/reports/pdf_rolling5_20260918.xlsx
@@ -1653,23 +1653,23 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-2086920061</v>
+        <v>-475695014</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>6.12%→4.99%</t>
+          <t>0.65%→0.44%</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>105→90</t>
+          <t>50→35</t>
         </is>
       </c>
     </row>
@@ -1681,23 +1681,23 @@
       <c r="E36" s="17" t="n"/>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
         <v>-15</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-475695014</v>
+        <v>-2086920061</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>0.65%→0.44%</t>
+          <t>6.12%→4.99%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>50→35</t>
+          <t>105→90</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260918.xlsx
+++ b/reports/pdf_rolling5_20260918.xlsx
@@ -1231,23 +1231,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-2238737618</v>
+        <v>-1227927313</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>3.78%→2.61%</t>
+          <t>6.44%→5.45%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>57→48</t>
+          <t>192→183</t>
         </is>
       </c>
     </row>
@@ -1259,23 +1259,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1227927313</v>
+        <v>-2238737618</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>6.44%→5.45%</t>
+          <t>3.78%→2.61%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>192→183</t>
+          <t>57→48</t>
         </is>
       </c>
     </row>
